--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_patch_dry_run_diff.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_patch_dry_run_diff.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,36 +436,42 @@
         <v>candidate_value</v>
       </c>
       <c r="K1" t="str">
+        <v>approved_value_raw</v>
+      </c>
+      <c r="L1" t="str">
         <v>approved_value</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>body_material_tech</v>
+      </c>
+      <c r="N1" t="str">
         <v>source_site</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>source_url</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>evidence_text</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>source_binding_key</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>rejected_candidate_value</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>year_scope_note</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>fitment_note</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>reviewer</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>review_note</v>
       </c>
     </row>
@@ -504,33 +510,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L2" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M2" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N2" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>SRED50014 | SRE5003 | 2021 | ANTARES DC R</v>
       </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
       <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S2" t="str">
+      <c r="U2" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T2" t="str">
+      <c r="V2" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U2" t="str">
+      <c r="W2" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -569,33 +581,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L3" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M3" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N3" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>SRED50015 | SRE5003 | 2021 | ANTARES DC L</v>
       </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
       <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S3" t="str">
+      <c r="U3" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T3" t="str">
+      <c r="V3" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U3" t="str">
+      <c r="W3" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -634,33 +652,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L4" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M4" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N4" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>SRED50016 | SRE5003 | 2021 | ANTARES DC HG R</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
       <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S4" t="str">
+      <c r="U4" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T4" t="str">
+      <c r="V4" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U4" t="str">
+      <c r="W4" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -699,33 +723,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L5" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M5" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N5" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O5" t="str">
+      <c r="Q5" t="str">
         <v>SRED50017 | SRE5003 | 2021 | ANTARES DC HG L</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
       <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S5" t="str">
+      <c r="U5" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T5" t="str">
+      <c r="V5" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U5" t="str">
+      <c r="W5" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -764,33 +794,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L6" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M6" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N6" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M6" t="str">
+      <c r="O6" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O6" t="str">
+      <c r="Q6" t="str">
         <v>SRED50018 | SRE5003 | 2021 | ANTARES DC XG R</v>
       </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
       <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S6" t="str">
+      <c r="U6" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T6" t="str">
+      <c r="V6" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U6" t="str">
+      <c r="W6" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -829,33 +865,39 @@
         <v>Hagane aluminum alloy body</v>
       </c>
       <c r="L7" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="M7" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N7" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M7" t="str">
+      <c r="O7" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
         <v>SRED50019 | SRE5003 | 2021 | ANTARES DC XG L</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
       <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S7" t="str">
+      <c r="U7" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T7" t="str">
+      <c r="V7" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U7" t="str">
+      <c r="W7" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -894,33 +936,39 @@
         <v>Magnesium</v>
       </c>
       <c r="L8" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M8" t="str">
+      <c r="O8" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="O8" t="str">
+      <c r="Q8" t="str">
         <v>SRED50020 | SRE5004 | 2023 | ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="P8" t="str">
+      <c r="R8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="S8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="R8" t="str">
+      <c r="T8" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S8" t="str">
+      <c r="U8" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="T8" t="str">
+      <c r="V8" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U8" t="str">
+      <c r="W8" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -959,33 +1007,39 @@
         <v>Magnesium</v>
       </c>
       <c r="L9" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M9" t="str">
+      <c r="O9" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="O9" t="str">
+      <c r="Q9" t="str">
         <v>SRED50021 | SRE5004 | 2023 | ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="P9" t="str">
+      <c r="R9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="S9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="R9" t="str">
+      <c r="T9" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S9" t="str">
+      <c r="U9" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="T9" t="str">
+      <c r="V9" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U9" t="str">
+      <c r="W9" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1024,33 +1078,39 @@
         <v>Magnesium</v>
       </c>
       <c r="L10" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M10" t="str">
+      <c r="O10" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="O10" t="str">
+      <c r="Q10" t="str">
         <v>SRED50022 | SRE5004 | 2023 | ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="P10" t="str">
+      <c r="R10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="S10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="R10" t="str">
+      <c r="T10" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S10" t="str">
+      <c r="U10" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="T10" t="str">
+      <c r="V10" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U10" t="str">
+      <c r="W10" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1089,33 +1149,39 @@
         <v>Magnesium</v>
       </c>
       <c r="L11" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M11" t="str">
+      <c r="O11" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="O11" t="str">
+      <c r="Q11" t="str">
         <v>SRED50023 | SRE5004 | 2023 | ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="P11" t="str">
+      <c r="R11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="S11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="R11" t="str">
+      <c r="T11" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="S11" t="str">
+      <c r="U11" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="T11" t="str">
+      <c r="V11" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U11" t="str">
+      <c r="W11" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1154,33 +1220,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L12" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M12" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N12" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M12" t="str">
+      <c r="O12" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O12" t="str">
+      <c r="Q12" t="str">
         <v>SRED50103 | SRE5015 | 2024 | Metanium DC 70</v>
       </c>
-      <c r="P12" t="str">
+      <c r="R12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="S12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R12" t="str">
+      <c r="T12" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S12" t="str">
+      <c r="U12" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T12" t="str">
+      <c r="V12" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U12" t="str">
+      <c r="W12" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1219,33 +1291,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L13" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M13" t="str">
+      <c r="O13" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O13" t="str">
+      <c r="Q13" t="str">
         <v>SRED50103 | SRE5015 | 2024 | Metanium DC 70</v>
       </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
       <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S13" t="str">
+      <c r="U13" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T13" t="str">
+      <c r="V13" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U13" t="str">
+      <c r="W13" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1284,33 +1362,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L14" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M14" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N14" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M14" t="str">
+      <c r="O14" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O14" t="str">
+      <c r="Q14" t="str">
         <v>SRED50104 | SRE5015 | 2024 | Metanium DC 71</v>
       </c>
-      <c r="P14" t="str">
+      <c r="R14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="S14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R14" t="str">
+      <c r="T14" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S14" t="str">
+      <c r="U14" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T14" t="str">
+      <c r="V14" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U14" t="str">
+      <c r="W14" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1349,33 +1433,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L15" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M15" t="str">
+      <c r="O15" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O15" t="str">
+      <c r="Q15" t="str">
         <v>SRED50104 | SRE5015 | 2024 | Metanium DC 71</v>
       </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
       <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S15" t="str">
+      <c r="U15" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T15" t="str">
+      <c r="V15" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U15" t="str">
+      <c r="W15" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1414,33 +1504,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L16" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M16" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N16" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M16" t="str">
+      <c r="O16" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O16" t="str">
+      <c r="Q16" t="str">
         <v>SRED50105 | SRE5015 | 2024 | Metanium DC 70HG</v>
       </c>
-      <c r="P16" t="str">
+      <c r="R16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="S16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R16" t="str">
+      <c r="T16" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S16" t="str">
+      <c r="U16" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T16" t="str">
+      <c r="V16" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U16" t="str">
+      <c r="W16" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1479,33 +1575,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L17" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M17" t="str">
+      <c r="O17" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O17" t="str">
+      <c r="Q17" t="str">
         <v>SRED50105 | SRE5015 | 2024 | Metanium DC 70HG</v>
       </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
       <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S17" t="str">
+      <c r="U17" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T17" t="str">
+      <c r="V17" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U17" t="str">
+      <c r="W17" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1544,33 +1646,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L18" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M18" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N18" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M18" t="str">
+      <c r="O18" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O18" t="str">
+      <c r="Q18" t="str">
         <v>SRED50106 | SRE5015 | 2024 | Metanium DC 71HG</v>
       </c>
-      <c r="P18" t="str">
+      <c r="R18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="S18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R18" t="str">
+      <c r="T18" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S18" t="str">
+      <c r="U18" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T18" t="str">
+      <c r="V18" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U18" t="str">
+      <c r="W18" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1609,33 +1717,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L19" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M19" t="str">
+      <c r="O19" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O19" t="str">
+      <c r="Q19" t="str">
         <v>SRED50106 | SRE5015 | 2024 | Metanium DC 71HG</v>
       </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
       <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S19" t="str">
+      <c r="U19" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T19" t="str">
+      <c r="V19" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U19" t="str">
+      <c r="W19" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1674,33 +1788,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L20" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M20" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N20" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M20" t="str">
+      <c r="O20" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O20" t="str">
+      <c r="Q20" t="str">
         <v>SRED50107 | SRE5015 | 2024 | Metanium DC 70XG</v>
       </c>
-      <c r="P20" t="str">
+      <c r="R20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="S20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R20" t="str">
+      <c r="T20" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S20" t="str">
+      <c r="U20" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T20" t="str">
+      <c r="V20" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U20" t="str">
+      <c r="W20" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1739,33 +1859,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L21" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M21" t="str">
+      <c r="O21" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O21" t="str">
+      <c r="Q21" t="str">
         <v>SRED50107 | SRE5015 | 2024 | Metanium DC 70XG</v>
       </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
       <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S21" t="str">
+      <c r="U21" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T21" t="str">
+      <c r="V21" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U21" t="str">
+      <c r="W21" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1804,33 +1930,39 @@
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
       <c r="L22" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M22" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="N22" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M22" t="str">
+      <c r="O22" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="O22" t="str">
+      <c r="Q22" t="str">
         <v>SRED50108 | SRE5015 | 2024 | Metanium DC 71XG</v>
       </c>
-      <c r="P22" t="str">
+      <c r="R22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="S22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="R22" t="str">
+      <c r="T22" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="S22" t="str">
+      <c r="U22" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="T22" t="str">
+      <c r="V22" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U22" t="str">
+      <c r="W22" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1869,33 +2001,39 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="L23" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M23" t="str">
+      <c r="O23" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="O23" t="str">
+      <c r="Q23" t="str">
         <v>SRED50108 | SRE5015 | 2024 | Metanium DC 71XG</v>
       </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
       <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="S23" t="str">
+      <c r="U23" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T23" t="str">
+      <c r="V23" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U23" t="str">
+      <c r="W23" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1934,33 +2072,39 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="L24" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="M24" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="N24" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M24" t="str">
+      <c r="O24" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="O24" t="str">
+      <c r="Q24" t="str">
         <v>SRED50131 | SRE5019 |  | CALCUTTA CONQUEST BFS HG RIGHT</v>
       </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
       <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="S24" t="str">
+      <c r="U24" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T24" t="str">
+      <c r="V24" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U24" t="str">
+      <c r="W24" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -1999,33 +2143,39 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="L25" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="M25" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="N25" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M25" t="str">
+      <c r="O25" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="O25" t="str">
+      <c r="Q25" t="str">
         <v>SRED50132 | SRE5019 |  | CALCUTTA CONQUEST BFS HG LEFT</v>
       </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
       <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="S25" t="str">
+      <c r="U25" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T25" t="str">
+      <c r="V25" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U25" t="str">
+      <c r="W25" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2064,33 +2214,39 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="L26" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="M26" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="N26" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M26" t="str">
+      <c r="O26" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="O26" t="str">
+      <c r="Q26" t="str">
         <v>SRED50133 | SRE5019 |  | CALCUTTA CONQUEST BFS XG RIGHT</v>
       </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
       <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="S26" t="str">
+      <c r="U26" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T26" t="str">
+      <c r="V26" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U26" t="str">
+      <c r="W26" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2129,33 +2285,39 @@
         <v>Fully machined aluminum body and side plates</v>
       </c>
       <c r="L27" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="M27" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="N27" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M27" t="str">
+      <c r="O27" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="O27" t="str">
+      <c r="Q27" t="str">
         <v>SRED50134 | SRE5019 |  | CALCUTTA CONQUEST BFS XG LEFT</v>
       </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
-        <v/>
-      </c>
       <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="S27" t="str">
+      <c r="U27" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="T27" t="str">
+      <c r="V27" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U27" t="str">
+      <c r="W27" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2194,33 +2356,39 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="L28" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M28" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N28" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M28" t="str">
+      <c r="O28" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
-      </c>
-      <c r="N28" t="str">
-        <v>Hagane body system</v>
-      </c>
-      <c r="O28" t="str">
-        <v>SRED50155 | SRE5025 |  | ALDEBARAN BFS HG R</v>
       </c>
       <c r="P28" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="Q28" t="str">
+        <v>SRED50155 | SRE5025 |  | ALDEBARAN BFS HG R</v>
+      </c>
+      <c r="R28" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="S28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="R28" t="str">
+      <c r="T28" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="S28" t="str">
+      <c r="U28" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="T28" t="str">
+      <c r="V28" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U28" t="str">
+      <c r="W28" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2259,33 +2427,39 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="L29" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M29" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N29" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M29" t="str">
+      <c r="O29" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
-      </c>
-      <c r="N29" t="str">
-        <v>Hagane body system</v>
-      </c>
-      <c r="O29" t="str">
-        <v>SRED50156 | SRE5025 |  | ALDEBARAN BFS HG L</v>
       </c>
       <c r="P29" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="Q29" t="str">
+        <v>SRED50156 | SRE5025 |  | ALDEBARAN BFS HG L</v>
+      </c>
+      <c r="R29" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="S29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="R29" t="str">
+      <c r="T29" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="S29" t="str">
+      <c r="U29" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="T29" t="str">
+      <c r="V29" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U29" t="str">
+      <c r="W29" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2324,33 +2498,39 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="L30" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M30" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N30" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M30" t="str">
+      <c r="O30" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
-      </c>
-      <c r="N30" t="str">
-        <v>Hagane body system</v>
-      </c>
-      <c r="O30" t="str">
-        <v>SRED50157 | SRE5025 |  | ALDEBARAN BFS XG R</v>
       </c>
       <c r="P30" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="Q30" t="str">
+        <v>SRED50157 | SRE5025 |  | ALDEBARAN BFS XG R</v>
+      </c>
+      <c r="R30" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="S30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="R30" t="str">
+      <c r="T30" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="S30" t="str">
+      <c r="U30" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="T30" t="str">
+      <c r="V30" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U30" t="str">
+      <c r="W30" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2389,46 +2569,52 @@
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
       <c r="L31" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="M31" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="N31" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="M31" t="str">
+      <c r="O31" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
-      </c>
-      <c r="N31" t="str">
-        <v>Hagane body system</v>
-      </c>
-      <c r="O31" t="str">
-        <v>SRED50158 | SRE5025 |  | ALDEBARAN BFS XG L</v>
       </c>
       <c r="P31" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="Q31" t="str">
+        <v>SRED50158 | SRE5025 |  | ALDEBARAN BFS XG L</v>
+      </c>
+      <c r="R31" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="S31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="R31" t="str">
+      <c r="T31" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="S31" t="str">
+      <c r="U31" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="T31" t="str">
+      <c r="V31" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="U31" t="str">
+      <c r="W31" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2456,24 +2642,27 @@
         <v>new_value</v>
       </c>
       <c r="I1" t="str">
+        <v>new_body_material_tech</v>
+      </c>
+      <c r="J1" t="str">
         <v>change_type</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>source_type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>candidate_value</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>rejected_candidate_value</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>year_scope_note</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>fitment_note</v>
       </c>
     </row>
@@ -2500,27 +2689,30 @@
         <v/>
       </c>
       <c r="H2" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I2" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J2" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K2" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I2" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J2" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2547,27 +2739,30 @@
         <v/>
       </c>
       <c r="H3" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I3" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J3" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K3" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I3" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J3" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
       <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2594,27 +2789,30 @@
         <v/>
       </c>
       <c r="H4" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I4" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J4" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K4" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I4" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J4" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2641,27 +2839,30 @@
         <v/>
       </c>
       <c r="H5" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I5" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J5" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K5" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I5" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J5" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2688,27 +2889,30 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I6" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J6" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K6" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I6" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J6" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2735,27 +2939,30 @@
         <v/>
       </c>
       <c r="H7" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="I7" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J7" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K7" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="I7" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J7" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Hagane aluminum alloy body</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2785,24 +2992,27 @@
         <v>Magnesium</v>
       </c>
       <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>manual</v>
-      </c>
-      <c r="K8" t="str">
-        <v>metal frames</v>
       </c>
       <c r="L8" t="str">
         <v>metal frames</v>
       </c>
       <c r="M8" t="str">
+        <v>metal frames</v>
+      </c>
+      <c r="N8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -2832,24 +3042,27 @@
         <v>Magnesium</v>
       </c>
       <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>manual</v>
-      </c>
-      <c r="K9" t="str">
-        <v>metal frames</v>
       </c>
       <c r="L9" t="str">
         <v>metal frames</v>
       </c>
       <c r="M9" t="str">
+        <v>metal frames</v>
+      </c>
+      <c r="N9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -2879,24 +3092,27 @@
         <v>Magnesium</v>
       </c>
       <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <v>manual</v>
-      </c>
-      <c r="K10" t="str">
-        <v>metal frames</v>
       </c>
       <c r="L10" t="str">
         <v>metal frames</v>
       </c>
       <c r="M10" t="str">
+        <v>metal frames</v>
+      </c>
+      <c r="N10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -2926,24 +3142,27 @@
         <v>Magnesium</v>
       </c>
       <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>manual</v>
-      </c>
-      <c r="K11" t="str">
-        <v>metal frames</v>
       </c>
       <c r="L11" t="str">
         <v>metal frames</v>
       </c>
       <c r="M11" t="str">
+        <v>metal frames</v>
+      </c>
+      <c r="N11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -2970,27 +3189,30 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I12" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J12" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <v>manual</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L12" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M12" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3020,24 +3242,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3064,27 +3289,30 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I14" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J14" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>manual</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L14" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M14" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3114,24 +3342,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3158,27 +3389,30 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I16" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J16" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>manual</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L16" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M16" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3208,24 +3442,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3252,27 +3489,30 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I18" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J18" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J18" t="str">
+      <c r="K18" t="str">
         <v>manual</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L18" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M18" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3302,24 +3542,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3346,27 +3589,30 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I20" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J20" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J20" t="str">
+      <c r="K20" t="str">
         <v>manual</v>
-      </c>
-      <c r="K20" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L20" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M20" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3396,24 +3642,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3440,27 +3689,30 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>CORESOLID BODY 镁合金一体成型</v>
+        <v>Magnesium</v>
       </c>
       <c r="I22" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="J22" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <v>manual</v>
-      </c>
-      <c r="K22" t="str">
-        <v>Core solid metal body</v>
       </c>
       <c r="L22" t="str">
         <v>Core solid metal body</v>
       </c>
       <c r="M22" t="str">
+        <v>Core solid metal body</v>
+      </c>
+      <c r="N22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3490,24 +3742,27 @@
         <v>Duralumin drive gear</v>
       </c>
       <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <v>whitelist</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3534,27 +3789,30 @@
         <v/>
       </c>
       <c r="H24" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="I24" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="J24" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K24" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="I24" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J24" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Fully machined aluminum body and side plates</v>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3581,27 +3839,30 @@
         <v/>
       </c>
       <c r="H25" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="I25" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="J25" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K25" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="I25" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J25" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Fully machined aluminum body and side plates</v>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3628,27 +3889,30 @@
         <v/>
       </c>
       <c r="H26" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="I26" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="J26" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K26" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="I26" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J26" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Fully machined aluminum body and side plates</v>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3675,27 +3939,30 @@
         <v/>
       </c>
       <c r="H27" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="I27" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="J27" t="str">
+        <v>fill_empty</v>
+      </c>
+      <c r="K27" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="L27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="I27" t="str">
-        <v>fill_empty</v>
-      </c>
-      <c r="J27" t="str">
-        <v>whitelist</v>
-      </c>
-      <c r="K27" t="str">
-        <v>Fully machined aluminum body and side plates</v>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3722,27 +3989,30 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>镁合金 (Magnesium) HAGANE 机身</v>
+        <v>Magnesium</v>
       </c>
       <c r="I28" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J28" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J28" t="str">
+      <c r="K28" t="str">
         <v>manual</v>
-      </c>
-      <c r="K28" t="str">
-        <v>Hagane body system</v>
       </c>
       <c r="L28" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="M28" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="N28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -3769,27 +4039,30 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>镁合金 (Magnesium) HAGANE 机身</v>
+        <v>Magnesium</v>
       </c>
       <c r="I29" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J29" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J29" t="str">
+      <c r="K29" t="str">
         <v>manual</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Hagane body system</v>
       </c>
       <c r="L29" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="M29" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="N29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -3816,27 +4089,30 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>镁合金 (Magnesium) HAGANE 机身</v>
+        <v>Magnesium</v>
       </c>
       <c r="I30" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J30" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>manual</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Hagane body system</v>
       </c>
       <c r="L30" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="M30" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="N30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -3863,33 +4139,36 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>镁合金 (Magnesium) HAGANE 机身</v>
+        <v>Magnesium</v>
       </c>
       <c r="I31" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="J31" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="J31" t="str">
+      <c r="K31" t="str">
         <v>manual</v>
-      </c>
-      <c r="K31" t="str">
-        <v>Hagane body system</v>
       </c>
       <c r="L31" t="str">
         <v>Hagane body system</v>
       </c>
       <c r="M31" t="str">
+        <v>Hagane body system</v>
+      </c>
+      <c r="N31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_patch_dry_run_diff.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_patch_dry_run_diff.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:AF31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,48 +430,75 @@
         <v>model_year</v>
       </c>
       <c r="I1" t="str">
+        <v>alias</v>
+      </c>
+      <c r="J1" t="str">
+        <v>version_signature</v>
+      </c>
+      <c r="K1" t="str">
         <v>sku</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>candidate_value</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>approved_value_raw</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>approved_value</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>body_material_tech</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
+        <v>body_material_official</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>body_material_tech_official</v>
+      </c>
+      <c r="R1" t="str">
+        <v>body_material_player</v>
+      </c>
+      <c r="S1" t="str">
+        <v>body_material_tech_player</v>
+      </c>
+      <c r="T1" t="str">
+        <v>client_display_priority</v>
+      </c>
+      <c r="U1" t="str">
+        <v>client_display_source</v>
+      </c>
+      <c r="V1" t="str">
+        <v>body_material_source_route</v>
+      </c>
+      <c r="W1" t="str">
         <v>source_site</v>
       </c>
-      <c r="O1" t="str">
+      <c r="X1" t="str">
         <v>source_url</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Y1" t="str">
         <v>evidence_text</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="Z1" t="str">
         <v>source_binding_key</v>
       </c>
-      <c r="R1" t="str">
+      <c r="AA1" t="str">
         <v>rejected_candidate_value</v>
       </c>
-      <c r="S1" t="str">
+      <c r="AB1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
-      <c r="T1" t="str">
+      <c r="AC1" t="str">
         <v>year_scope_note</v>
       </c>
-      <c r="U1" t="str">
+      <c r="AD1" t="str">
         <v>fitment_note</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AE1" t="str">
         <v>reviewer</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AF1" t="str">
         <v>review_note</v>
       </c>
     </row>
@@ -501,48 +528,75 @@
         <v>2021</v>
       </c>
       <c r="I2" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J2" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K2" t="str">
         <v>ANTARES DC R</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S2" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T2" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U2" t="str">
+        <v>player</v>
+      </c>
+      <c r="V2" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W2" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O2" t="str">
+      <c r="X2" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Y2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Z2" t="str">
         <v>SRED50014 | SRE5003 | 2021 | ANTARES DC R</v>
       </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U2" t="str">
+      <c r="AD2" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V2" t="str">
+      <c r="AE2" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AF2" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -572,48 +626,75 @@
         <v>2021</v>
       </c>
       <c r="I3" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J3" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K3" t="str">
         <v>ANTARES DC L</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S3" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T3" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U3" t="str">
+        <v>player</v>
+      </c>
+      <c r="V3" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W3" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O3" t="str">
+      <c r="X3" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Y3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Z3" t="str">
         <v>SRED50015 | SRE5003 | 2021 | ANTARES DC L</v>
       </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U3" t="str">
+      <c r="AD3" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V3" t="str">
+      <c r="AE3" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W3" t="str">
+      <c r="AF3" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -643,48 +724,75 @@
         <v>2021</v>
       </c>
       <c r="I4" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J4" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K4" t="str">
         <v>ANTARES DC HG R</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S4" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T4" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U4" t="str">
+        <v>player</v>
+      </c>
+      <c r="V4" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W4" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O4" t="str">
+      <c r="X4" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Y4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="Z4" t="str">
         <v>SRED50016 | SRE5003 | 2021 | ANTARES DC HG R</v>
       </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U4" t="str">
+      <c r="AD4" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V4" t="str">
+      <c r="AE4" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W4" t="str">
+      <c r="AF4" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -714,48 +822,75 @@
         <v>2021</v>
       </c>
       <c r="I5" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J5" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K5" t="str">
         <v>ANTARES DC HG L</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K5" t="str">
+      <c r="M5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L5" t="str">
+      <c r="N5" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S5" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T5" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U5" t="str">
+        <v>player</v>
+      </c>
+      <c r="V5" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W5" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O5" t="str">
+      <c r="X5" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Y5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="Z5" t="str">
         <v>SRED50017 | SRE5003 | 2021 | ANTARES DC HG L</v>
       </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U5" t="str">
+      <c r="AD5" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V5" t="str">
+      <c r="AE5" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W5" t="str">
+      <c r="AF5" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -785,48 +920,75 @@
         <v>2021</v>
       </c>
       <c r="I6" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J6" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K6" t="str">
         <v>ANTARES DC XG R</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K6" t="str">
+      <c r="M6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L6" t="str">
+      <c r="N6" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M6" t="str">
+      <c r="O6" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S6" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T6" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U6" t="str">
+        <v>player</v>
+      </c>
+      <c r="V6" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W6" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O6" t="str">
+      <c r="X6" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Y6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Z6" t="str">
         <v>SRED50018 | SRE5003 | 2021 | ANTARES DC XG R</v>
       </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U6" t="str">
+      <c r="AD6" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V6" t="str">
+      <c r="AE6" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W6" t="str">
+      <c r="AF6" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -856,48 +1018,75 @@
         <v>2021</v>
       </c>
       <c r="I7" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J7" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="K7" t="str">
         <v>ANTARES DC XG L</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="K7" t="str">
+      <c r="M7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="L7" t="str">
+      <c r="N7" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="M7" t="str">
+      <c r="O7" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>Aluminum alloy</v>
+      </c>
+      <c r="S7" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T7" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U7" t="str">
+        <v>player</v>
+      </c>
+      <c r="V7" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W7" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O7" t="str">
+      <c r="X7" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Y7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="Z7" t="str">
         <v>SRED50019 | SRE5003 | 2021 | ANTARES DC XG L</v>
       </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U7" t="str">
+      <c r="AD7" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V7" t="str">
+      <c r="AE7" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W7" t="str">
+      <c r="AF7" t="str">
         <v>Correct and acceptable, but this appears to describe the 2021 ANTARES DC generation.</v>
       </c>
     </row>
@@ -927,48 +1116,75 @@
         <v>2023</v>
       </c>
       <c r="I8" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="J8" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="K8" t="str">
         <v>ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="K8" t="str">
+      <c r="M8" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="L8" t="str">
+      <c r="N8" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U8" t="str">
+        <v>player</v>
+      </c>
+      <c r="V8" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W8" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O8" t="str">
+      <c r="X8" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Y8" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Z8" t="str">
         <v>SRED50020 | SRE5004 | 2023 | ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="R8" t="str">
+      <c r="AA8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="S8" t="str">
+      <c r="AB8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="T8" t="str">
+      <c r="AC8" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U8" t="str">
+      <c r="AD8" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="V8" t="str">
+      <c r="AE8" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W8" t="str">
+      <c r="AF8" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -998,48 +1214,75 @@
         <v>2023</v>
       </c>
       <c r="I9" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="J9" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="K9" t="str">
         <v>ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="K9" t="str">
+      <c r="M9" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="L9" t="str">
+      <c r="N9" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U9" t="str">
+        <v>player</v>
+      </c>
+      <c r="V9" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W9" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O9" t="str">
+      <c r="X9" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Y9" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="Z9" t="str">
         <v>SRED50021 | SRE5004 | 2023 | ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="R9" t="str">
+      <c r="AA9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="S9" t="str">
+      <c r="AB9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="T9" t="str">
+      <c r="AC9" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U9" t="str">
+      <c r="AD9" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="V9" t="str">
+      <c r="AE9" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W9" t="str">
+      <c r="AF9" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1069,48 +1312,75 @@
         <v>2023</v>
       </c>
       <c r="I10" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="J10" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="K10" t="str">
         <v>ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="K10" t="str">
+      <c r="M10" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="L10" t="str">
+      <c r="N10" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U10" t="str">
+        <v>player</v>
+      </c>
+      <c r="V10" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W10" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O10" t="str">
+      <c r="X10" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Y10" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="Z10" t="str">
         <v>SRED50022 | SRE5004 | 2023 | ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="R10" t="str">
+      <c r="AA10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="S10" t="str">
+      <c r="AB10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="T10" t="str">
+      <c r="AC10" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U10" t="str">
+      <c r="AD10" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="V10" t="str">
+      <c r="AE10" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W10" t="str">
+      <c r="AF10" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1140,48 +1410,75 @@
         <v>2023</v>
       </c>
       <c r="I11" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="J11" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="K11" t="str">
         <v>ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="K11" t="str">
+      <c r="M11" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="L11" t="str">
+      <c r="N11" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U11" t="str">
+        <v>player</v>
+      </c>
+      <c r="V11" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W11" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O11" t="str">
+      <c r="X11" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Y11" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="Z11" t="str">
         <v>SRED50023 | SRE5004 | 2023 | ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="R11" t="str">
+      <c r="AA11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="S11" t="str">
+      <c r="AB11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="T11" t="str">
+      <c r="AC11" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="U11" t="str">
+      <c r="AD11" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
-      <c r="V11" t="str">
+      <c r="AE11" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W11" t="str">
+      <c r="AF11" t="str">
         <v>Reject candidate 'metal frames' because it is not a specific material.</v>
       </c>
     </row>
@@ -1211,48 +1508,75 @@
         <v>2024</v>
       </c>
       <c r="I12" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K12" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K12" t="str">
+      <c r="M12" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L12" t="str">
+      <c r="N12" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M12" t="str">
+      <c r="O12" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S12" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T12" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U12" t="str">
+        <v>player</v>
+      </c>
+      <c r="V12" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W12" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O12" t="str">
+      <c r="X12" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Y12" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="Z12" t="str">
         <v>SRED50103 | SRE5015 | 2024 | Metanium DC 70</v>
       </c>
-      <c r="R12" t="str">
+      <c r="AA12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S12" t="str">
+      <c r="AB12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T12" t="str">
+      <c r="AC12" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U12" t="str">
+      <c r="AD12" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V12" t="str">
+      <c r="AE12" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W12" t="str">
+      <c r="AF12" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1282,48 +1606,75 @@
         <v>2024</v>
       </c>
       <c r="I13" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K13" t="str">
         <v>Metanium DC 70</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L13" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N13" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U13" t="str">
+        <v>player</v>
+      </c>
+      <c r="V13" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W13" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O13" t="str">
+      <c r="X13" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Y13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="Z13" t="str">
         <v>SRED50103 | SRE5015 | 2024 | Metanium DC 70</v>
       </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str">
-        <v/>
-      </c>
-      <c r="T13" t="str">
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U13" t="str">
+      <c r="AD13" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V13" t="str">
+      <c r="AE13" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W13" t="str">
+      <c r="AF13" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1353,48 +1704,75 @@
         <v>2024</v>
       </c>
       <c r="I14" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K14" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K14" t="str">
+      <c r="M14" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L14" t="str">
+      <c r="N14" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M14" t="str">
+      <c r="O14" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S14" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T14" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U14" t="str">
+        <v>player</v>
+      </c>
+      <c r="V14" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W14" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O14" t="str">
+      <c r="X14" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Y14" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="Z14" t="str">
         <v>SRED50104 | SRE5015 | 2024 | Metanium DC 71</v>
       </c>
-      <c r="R14" t="str">
+      <c r="AA14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S14" t="str">
+      <c r="AB14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T14" t="str">
+      <c r="AC14" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U14" t="str">
+      <c r="AD14" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V14" t="str">
+      <c r="AE14" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W14" t="str">
+      <c r="AF14" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1424,48 +1802,75 @@
         <v>2024</v>
       </c>
       <c r="I15" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K15" t="str">
         <v>Metanium DC 71</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L15" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N15" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U15" t="str">
+        <v>player</v>
+      </c>
+      <c r="V15" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W15" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O15" t="str">
+      <c r="X15" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Y15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="Z15" t="str">
         <v>SRED50104 | SRE5015 | 2024 | Metanium DC 71</v>
       </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U15" t="str">
+      <c r="AD15" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V15" t="str">
+      <c r="AE15" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W15" t="str">
+      <c r="AF15" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1495,48 +1900,75 @@
         <v>2024</v>
       </c>
       <c r="I16" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K16" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K16" t="str">
+      <c r="M16" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L16" t="str">
+      <c r="N16" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M16" t="str">
+      <c r="O16" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S16" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T16" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U16" t="str">
+        <v>player</v>
+      </c>
+      <c r="V16" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W16" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O16" t="str">
+      <c r="X16" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Y16" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="Z16" t="str">
         <v>SRED50105 | SRE5015 | 2024 | Metanium DC 70HG</v>
       </c>
-      <c r="R16" t="str">
+      <c r="AA16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S16" t="str">
+      <c r="AB16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T16" t="str">
+      <c r="AC16" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U16" t="str">
+      <c r="AD16" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V16" t="str">
+      <c r="AE16" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W16" t="str">
+      <c r="AF16" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1566,48 +1998,75 @@
         <v>2024</v>
       </c>
       <c r="I17" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K17" t="str">
         <v>Metanium DC 70HG</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L17" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N17" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U17" t="str">
+        <v>player</v>
+      </c>
+      <c r="V17" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W17" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O17" t="str">
+      <c r="X17" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Y17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="Z17" t="str">
         <v>SRED50105 | SRE5015 | 2024 | Metanium DC 70HG</v>
       </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U17" t="str">
+      <c r="AD17" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V17" t="str">
+      <c r="AE17" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W17" t="str">
+      <c r="AF17" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1637,48 +2096,75 @@
         <v>2024</v>
       </c>
       <c r="I18" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K18" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K18" t="str">
+      <c r="M18" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L18" t="str">
+      <c r="N18" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M18" t="str">
+      <c r="O18" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S18" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T18" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U18" t="str">
+        <v>player</v>
+      </c>
+      <c r="V18" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W18" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O18" t="str">
+      <c r="X18" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Y18" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="Z18" t="str">
         <v>SRED50106 | SRE5015 | 2024 | Metanium DC 71HG</v>
       </c>
-      <c r="R18" t="str">
+      <c r="AA18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S18" t="str">
+      <c r="AB18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T18" t="str">
+      <c r="AC18" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U18" t="str">
+      <c r="AD18" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V18" t="str">
+      <c r="AE18" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W18" t="str">
+      <c r="AF18" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1708,48 +2194,75 @@
         <v>2024</v>
       </c>
       <c r="I19" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K19" t="str">
         <v>Metanium DC 71HG</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L19" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N19" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U19" t="str">
+        <v>player</v>
+      </c>
+      <c r="V19" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W19" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O19" t="str">
+      <c r="X19" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Y19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="Z19" t="str">
         <v>SRED50106 | SRE5015 | 2024 | Metanium DC 71HG</v>
       </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <v/>
-      </c>
-      <c r="T19" t="str">
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U19" t="str">
+      <c r="AD19" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V19" t="str">
+      <c r="AE19" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W19" t="str">
+      <c r="AF19" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1779,48 +2292,75 @@
         <v>2024</v>
       </c>
       <c r="I20" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K20" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K20" t="str">
+      <c r="M20" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L20" t="str">
+      <c r="N20" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M20" t="str">
+      <c r="O20" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S20" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T20" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U20" t="str">
+        <v>player</v>
+      </c>
+      <c r="V20" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W20" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O20" t="str">
+      <c r="X20" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Y20" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="Z20" t="str">
         <v>SRED50107 | SRE5015 | 2024 | Metanium DC 70XG</v>
       </c>
-      <c r="R20" t="str">
+      <c r="AA20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S20" t="str">
+      <c r="AB20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T20" t="str">
+      <c r="AC20" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U20" t="str">
+      <c r="AD20" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V20" t="str">
+      <c r="AE20" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W20" t="str">
+      <c r="AF20" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1850,48 +2390,75 @@
         <v>2024</v>
       </c>
       <c r="I21" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K21" t="str">
         <v>Metanium DC 70XG</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L21" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N21" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U21" t="str">
+        <v>player</v>
+      </c>
+      <c r="V21" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W21" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O21" t="str">
+      <c r="X21" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Y21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="Z21" t="str">
         <v>SRED50107 | SRE5015 | 2024 | Metanium DC 70XG</v>
       </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str">
-        <v/>
-      </c>
-      <c r="T21" t="str">
+      <c r="AA21" t="str">
+        <v/>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U21" t="str">
+      <c r="AD21" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V21" t="str">
+      <c r="AE21" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W21" t="str">
+      <c r="AF21" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -1921,48 +2488,75 @@
         <v>2024</v>
       </c>
       <c r="I22" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K22" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="K22" t="str">
+      <c r="M22" t="str">
         <v>CORESOLID BODY 镁合金一体成型</v>
       </c>
-      <c r="L22" t="str">
+      <c r="N22" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M22" t="str">
+      <c r="O22" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S22" t="str">
+        <v>CORESOLID BODY / 一体成型</v>
+      </c>
+      <c r="T22" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U22" t="str">
+        <v>player</v>
+      </c>
+      <c r="V22" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W22" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O22" t="str">
+      <c r="X22" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Y22" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="Z22" t="str">
         <v>SRED50108 | SRE5015 | 2024 | Metanium DC 71XG</v>
       </c>
-      <c r="R22" t="str">
+      <c r="AA22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="S22" t="str">
+      <c r="AB22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="T22" t="str">
+      <c r="AC22" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="U22" t="str">
+      <c r="AD22" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
-      <c r="V22" t="str">
+      <c r="AE22" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W22" t="str">
+      <c r="AF22" t="str">
         <v>Reject candidate 'Core solid metal body' because it is a technology phrase, not a precise material expression.</v>
       </c>
     </row>
@@ -1992,48 +2586,75 @@
         <v>2024</v>
       </c>
       <c r="I23" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="K23" t="str">
         <v>Metanium DC 71XG</v>
-      </c>
-      <c r="J23" t="str">
-        <v>Duralumin drive gear</v>
-      </c>
-      <c r="K23" t="str">
-        <v>Duralumin drive gear</v>
       </c>
       <c r="L23" t="str">
         <v>Duralumin drive gear</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Duralumin drive gear</v>
       </c>
       <c r="N23" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v>Duralumin drive gear</v>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U23" t="str">
+        <v>player</v>
+      </c>
+      <c r="V23" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W23" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O23" t="str">
+      <c r="X23" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Y23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="Z23" t="str">
         <v>SRED50108 | SRE5015 | 2024 | Metanium DC 71XG</v>
       </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="U23" t="str">
+      <c r="AD23" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V23" t="str">
+      <c r="AE23" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W23" t="str">
+      <c r="AF23" t="str">
         <v>Correct and acceptable, but keep year awareness for other Metanium DC generations.</v>
       </c>
     </row>
@@ -2060,51 +2681,78 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I24" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J24" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K24" t="str">
         <v>CALCUTTA CONQUEST BFS HG RIGHT</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K24" t="str">
+      <c r="M24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="L24" t="str">
+      <c r="N24" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="M24" t="str">
+      <c r="O24" t="str">
         <v>全加工</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="S24" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="T24" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U24" t="str">
+        <v>player</v>
+      </c>
+      <c r="V24" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W24" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O24" t="str">
+      <c r="X24" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Y24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="Q24" t="str">
-        <v>SRED50131 | SRE5019 |  | CALCUTTA CONQUEST BFS HG RIGHT</v>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
+      <c r="Z24" t="str">
+        <v>SRED50131 | SRE5019 | 2026 | CALCUTTA CONQUEST BFS HG RIGHT</v>
+      </c>
+      <c r="AA24" t="str">
+        <v/>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+      <c r="AC24" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="U24" t="str">
+      <c r="AD24" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V24" t="str">
+      <c r="AE24" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W24" t="str">
+      <c r="AF24" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2131,51 +2779,78 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I25" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J25" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K25" t="str">
         <v>CALCUTTA CONQUEST BFS HG LEFT</v>
       </c>
-      <c r="J25" t="str">
+      <c r="L25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K25" t="str">
+      <c r="M25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="L25" t="str">
+      <c r="N25" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="M25" t="str">
+      <c r="O25" t="str">
         <v>全加工</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="S25" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="T25" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U25" t="str">
+        <v>player</v>
+      </c>
+      <c r="V25" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W25" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O25" t="str">
+      <c r="X25" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Y25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="Q25" t="str">
-        <v>SRED50132 | SRE5019 |  | CALCUTTA CONQUEST BFS HG LEFT</v>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
+      <c r="Z25" t="str">
+        <v>SRED50132 | SRE5019 | 2026 | CALCUTTA CONQUEST BFS HG LEFT</v>
+      </c>
+      <c r="AA25" t="str">
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+      <c r="AC25" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="U25" t="str">
+      <c r="AD25" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V25" t="str">
+      <c r="AE25" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W25" t="str">
+      <c r="AF25" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2202,51 +2877,78 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I26" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J26" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K26" t="str">
         <v>CALCUTTA CONQUEST BFS XG RIGHT</v>
       </c>
-      <c r="J26" t="str">
+      <c r="L26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K26" t="str">
+      <c r="M26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="L26" t="str">
+      <c r="N26" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="M26" t="str">
+      <c r="O26" t="str">
         <v>全加工</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="S26" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="T26" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U26" t="str">
+        <v>player</v>
+      </c>
+      <c r="V26" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W26" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O26" t="str">
+      <c r="X26" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Y26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="Q26" t="str">
-        <v>SRED50133 | SRE5019 |  | CALCUTTA CONQUEST BFS XG RIGHT</v>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
+      <c r="Z26" t="str">
+        <v>SRED50133 | SRE5019 | 2026 | CALCUTTA CONQUEST BFS XG RIGHT</v>
+      </c>
+      <c r="AA26" t="str">
+        <v/>
+      </c>
+      <c r="AB26" t="str">
+        <v/>
+      </c>
+      <c r="AC26" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="U26" t="str">
+      <c r="AD26" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V26" t="str">
+      <c r="AE26" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W26" t="str">
+      <c r="AF26" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2273,51 +2975,78 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I27" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="J27" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K27" t="str">
         <v>CALCUTTA CONQUEST BFS XG LEFT</v>
       </c>
-      <c r="J27" t="str">
+      <c r="L27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="K27" t="str">
+      <c r="M27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="L27" t="str">
+      <c r="N27" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="M27" t="str">
+      <c r="O27" t="str">
         <v>全加工</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v>Aluminum</v>
+      </c>
+      <c r="S27" t="str">
+        <v>全加工</v>
+      </c>
+      <c r="T27" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U27" t="str">
+        <v>player</v>
+      </c>
+      <c r="V27" t="str">
+        <v>whitelist</v>
+      </c>
+      <c r="W27" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O27" t="str">
+      <c r="X27" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Y27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="Q27" t="str">
-        <v>SRED50134 | SRE5019 |  | CALCUTTA CONQUEST BFS XG LEFT</v>
-      </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <v/>
-      </c>
-      <c r="T27" t="str">
+      <c r="Z27" t="str">
+        <v>SRED50134 | SRE5019 | 2026 | CALCUTTA CONQUEST BFS XG LEFT</v>
+      </c>
+      <c r="AA27" t="str">
+        <v/>
+      </c>
+      <c r="AB27" t="str">
+        <v/>
+      </c>
+      <c r="AC27" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="U27" t="str">
+      <c r="AD27" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
-      <c r="V27" t="str">
+      <c r="AE27" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W27" t="str">
+      <c r="AF27" t="str">
         <v>Correct and acceptable, but keep year awareness for future generations.</v>
       </c>
     </row>
@@ -2344,51 +3073,78 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I28" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="J28" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K28" t="str">
         <v>ALDEBARAN BFS HG R</v>
       </c>
-      <c r="J28" t="str">
+      <c r="L28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K28" t="str">
+      <c r="M28" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="L28" t="str">
+      <c r="N28" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M28" t="str">
+      <c r="O28" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S28" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T28" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U28" t="str">
+        <v>player</v>
+      </c>
+      <c r="V28" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W28" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O28" t="str">
+      <c r="X28" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Y28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="Q28" t="str">
-        <v>SRED50155 | SRE5025 |  | ALDEBARAN BFS HG R</v>
-      </c>
-      <c r="R28" t="str">
+      <c r="Z28" t="str">
+        <v>SRED50155 | SRE5025 | 2026 | ALDEBARAN BFS HG R</v>
+      </c>
+      <c r="AA28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="S28" t="str">
+      <c r="AB28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="T28" t="str">
+      <c r="AC28" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="U28" t="str">
+      <c r="AD28" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="V28" t="str">
+      <c r="AE28" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W28" t="str">
+      <c r="AF28" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2415,51 +3171,78 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I29" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="J29" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K29" t="str">
         <v>ALDEBARAN BFS HG L</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K29" t="str">
+      <c r="M29" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="L29" t="str">
+      <c r="N29" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M29" t="str">
+      <c r="O29" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S29" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T29" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U29" t="str">
+        <v>player</v>
+      </c>
+      <c r="V29" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W29" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O29" t="str">
+      <c r="X29" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Y29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="Q29" t="str">
-        <v>SRED50156 | SRE5025 |  | ALDEBARAN BFS HG L</v>
-      </c>
-      <c r="R29" t="str">
+      <c r="Z29" t="str">
+        <v>SRED50156 | SRE5025 | 2026 | ALDEBARAN BFS HG L</v>
+      </c>
+      <c r="AA29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="S29" t="str">
+      <c r="AB29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="T29" t="str">
+      <c r="AC29" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="U29" t="str">
+      <c r="AD29" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="V29" t="str">
+      <c r="AE29" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W29" t="str">
+      <c r="AF29" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2486,51 +3269,78 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I30" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="J30" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K30" t="str">
         <v>ALDEBARAN BFS XG R</v>
       </c>
-      <c r="J30" t="str">
+      <c r="L30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K30" t="str">
+      <c r="M30" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="L30" t="str">
+      <c r="N30" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M30" t="str">
+      <c r="O30" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S30" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T30" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U30" t="str">
+        <v>player</v>
+      </c>
+      <c r="V30" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W30" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O30" t="str">
+      <c r="X30" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Y30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="Q30" t="str">
-        <v>SRED50157 | SRE5025 |  | ALDEBARAN BFS XG R</v>
-      </c>
-      <c r="R30" t="str">
+      <c r="Z30" t="str">
+        <v>SRED50157 | SRE5025 | 2026 | ALDEBARAN BFS XG R</v>
+      </c>
+      <c r="AA30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="S30" t="str">
+      <c r="AB30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="T30" t="str">
+      <c r="AC30" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="U30" t="str">
+      <c r="AD30" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="V30" t="str">
+      <c r="AE30" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W30" t="str">
+      <c r="AF30" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
@@ -2557,64 +3367,91 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="I31" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="J31" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="K31" t="str">
         <v>ALDEBARAN BFS XG L</v>
       </c>
-      <c r="J31" t="str">
+      <c r="L31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="K31" t="str">
+      <c r="M31" t="str">
         <v>镁合金 (Magnesium) HAGANE 机身</v>
       </c>
-      <c r="L31" t="str">
+      <c r="N31" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="M31" t="str">
+      <c r="O31" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v>Magnesium</v>
+      </c>
+      <c r="S31" t="str">
+        <v>HAGANE 机身</v>
+      </c>
+      <c r="T31" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="U31" t="str">
+        <v>player</v>
+      </c>
+      <c r="V31" t="str">
+        <v>manual</v>
+      </c>
+      <c r="W31" t="str">
         <v>JapanTackle</v>
       </c>
-      <c r="O31" t="str">
+      <c r="X31" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Y31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="Q31" t="str">
-        <v>SRED50158 | SRE5025 |  | ALDEBARAN BFS XG L</v>
-      </c>
-      <c r="R31" t="str">
+      <c r="Z31" t="str">
+        <v>SRED50158 | SRE5025 | 2026 | ALDEBARAN BFS XG L</v>
+      </c>
+      <c r="AA31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="S31" t="str">
+      <c r="AB31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="T31" t="str">
+      <c r="AC31" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="U31" t="str">
+      <c r="AD31" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
-      <c r="V31" t="str">
+      <c r="AE31" t="str">
         <v>user_review_2026-04-16</v>
       </c>
-      <c r="W31" t="str">
+      <c r="AF31" t="str">
         <v>Reject candidate 'Hagane body system' because it is a technology/system term, not the actual material wording.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:T31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2630,39 +3467,51 @@
         <v>model_year</v>
       </c>
       <c r="E1" t="str">
+        <v>alias</v>
+      </c>
+      <c r="F1" t="str">
+        <v>version_signature</v>
+      </c>
+      <c r="G1" t="str">
         <v>sku</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>field_key</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>old_value</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>new_value</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>new_body_material_tech</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>client_display_source</v>
+      </c>
+      <c r="M1" t="str">
+        <v>client_display_priority</v>
+      </c>
+      <c r="N1" t="str">
         <v>change_type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
         <v>source_type</v>
       </c>
-      <c r="L1" t="str">
+      <c r="P1" t="str">
         <v>candidate_value</v>
       </c>
-      <c r="M1" t="str">
+      <c r="Q1" t="str">
         <v>rejected_candidate_value</v>
       </c>
-      <c r="N1" t="str">
+      <c r="R1" t="str">
         <v>rejected_candidate_reason</v>
       </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
         <v>year_scope_note</v>
       </c>
-      <c r="P1" t="str">
+      <c r="T1" t="str">
         <v>fitment_note</v>
       </c>
     </row>
@@ -2680,39 +3529,51 @@
         <v>2021</v>
       </c>
       <c r="E2" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G2" t="str">
         <v>ANTARES DC R</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>body_material</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v>player</v>
+      </c>
+      <c r="M2" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N2" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K2" t="str">
+      <c r="O2" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L2" t="str">
+      <c r="P2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P2" t="str">
+      <c r="T2" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2730,39 +3591,51 @@
         <v>2021</v>
       </c>
       <c r="E3" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F3" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G3" t="str">
         <v>ANTARES DC L</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>body_material</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v>player</v>
+      </c>
+      <c r="M3" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N3" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K3" t="str">
+      <c r="O3" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L3" t="str">
+      <c r="P3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P3" t="str">
+      <c r="T3" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2780,39 +3653,51 @@
         <v>2021</v>
       </c>
       <c r="E4" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F4" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G4" t="str">
         <v>ANTARES DC HG R</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>body_material</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v>player</v>
+      </c>
+      <c r="M4" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N4" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K4" t="str">
+      <c r="O4" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L4" t="str">
+      <c r="P4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P4" t="str">
+      <c r="T4" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2830,39 +3715,51 @@
         <v>2021</v>
       </c>
       <c r="E5" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F5" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G5" t="str">
         <v>ANTARES DC HG L</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>body_material</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
+        <v>player</v>
+      </c>
+      <c r="M5" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N5" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K5" t="str">
+      <c r="O5" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L5" t="str">
+      <c r="P5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P5" t="str">
+      <c r="T5" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2880,39 +3777,51 @@
         <v>2021</v>
       </c>
       <c r="E6" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F6" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G6" t="str">
         <v>ANTARES DC XG R</v>
       </c>
-      <c r="F6" t="str">
+      <c r="H6" t="str">
         <v>body_material</v>
       </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
+        <v>player</v>
+      </c>
+      <c r="M6" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N6" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K6" t="str">
+      <c r="O6" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L6" t="str">
+      <c r="P6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P6" t="str">
+      <c r="T6" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2930,39 +3839,51 @@
         <v>2021</v>
       </c>
       <c r="E7" t="str">
+        <v>21 Antares DC Japan model 2021- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F7" t="str">
+        <v>ANTARES DC | 2021 | 6 sku variants</v>
+      </c>
+      <c r="G7" t="str">
         <v>ANTARES DC XG L</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>body_material</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="I7" t="str">
+      <c r="K7" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
+        <v>player</v>
+      </c>
+      <c r="M7" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N7" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K7" t="str">
+      <c r="O7" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L7" t="str">
+      <c r="P7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v>Bind to 2021 ANTARES DC. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P7" t="str">
+      <c r="T7" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -2980,39 +3901,51 @@
         <v>2023</v>
       </c>
       <c r="E8" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="F8" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="G8" t="str">
         <v>ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="F8" t="str">
+      <c r="H8" t="str">
         <v>body_material</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>player</v>
+      </c>
+      <c r="M8" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N8" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K8" t="str">
+      <c r="O8" t="str">
         <v>manual</v>
       </c>
-      <c r="L8" t="str">
+      <c r="P8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="M8" t="str">
+      <c r="Q8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="N8" t="str">
+      <c r="R8" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="O8" t="str">
+      <c r="S8" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P8" t="str">
+      <c r="T8" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -3030,39 +3963,51 @@
         <v>2023</v>
       </c>
       <c r="E9" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="F9" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="G9" t="str">
         <v>ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v>body_material</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>player</v>
+      </c>
+      <c r="M9" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N9" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K9" t="str">
+      <c r="O9" t="str">
         <v>manual</v>
       </c>
-      <c r="L9" t="str">
+      <c r="P9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="M9" t="str">
+      <c r="Q9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="N9" t="str">
+      <c r="R9" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="O9" t="str">
+      <c r="S9" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P9" t="str">
+      <c r="T9" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -3080,39 +4025,51 @@
         <v>2023</v>
       </c>
       <c r="E10" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="F10" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="G10" t="str">
         <v>ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="F10" t="str">
+      <c r="H10" t="str">
         <v>body_material</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>player</v>
+      </c>
+      <c r="M10" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N10" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K10" t="str">
+      <c r="O10" t="str">
         <v>manual</v>
       </c>
-      <c r="L10" t="str">
+      <c r="P10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="M10" t="str">
+      <c r="Q10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="N10" t="str">
+      <c r="R10" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="O10" t="str">
+      <c r="S10" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P10" t="str">
+      <c r="T10" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -3130,39 +4087,51 @@
         <v>2023</v>
       </c>
       <c r="E11" t="str">
+        <v>23 Antares DC MD Monster Drive 2023- - Casting Reels</v>
+      </c>
+      <c r="F11" t="str">
+        <v>ANTARES DC MD | 2023 | 4 sku variants</v>
+      </c>
+      <c r="G11" t="str">
         <v>ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v>body_material</v>
       </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>player</v>
+      </c>
+      <c r="M11" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N11" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K11" t="str">
+      <c r="O11" t="str">
         <v>manual</v>
       </c>
-      <c r="L11" t="str">
+      <c r="P11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="M11" t="str">
+      <c r="Q11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="N11" t="str">
+      <c r="R11" t="str">
         <v>Candidate is generic wording, not an explicit material field.</v>
       </c>
-      <c r="O11" t="str">
+      <c r="S11" t="str">
         <v>Bind to 2023 ANTARES DC MD. Same-series body material may differ across other years.</v>
       </c>
-      <c r="P11" t="str">
+      <c r="T11" t="str">
         <v>Manual override based on review knowledge: 2023 ANTARES DC MD body material is Magnesium.</v>
       </c>
     </row>
@@ -3180,39 +4149,51 @@
         <v>2024</v>
       </c>
       <c r="E12" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G12" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="F12" t="str">
+      <c r="H12" t="str">
         <v>body_material</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I12" t="str">
+      <c r="K12" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
+        <v>player</v>
+      </c>
+      <c r="M12" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N12" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K12" t="str">
+      <c r="O12" t="str">
         <v>manual</v>
       </c>
-      <c r="L12" t="str">
+      <c r="P12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M12" t="str">
+      <c r="Q12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N12" t="str">
+      <c r="R12" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O12" t="str">
+      <c r="S12" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P12" t="str">
+      <c r="T12" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3230,39 +4211,51 @@
         <v>2024</v>
       </c>
       <c r="E13" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G13" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="F13" t="str">
+      <c r="H13" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>player</v>
+      </c>
+      <c r="M13" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N13" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K13" t="str">
+      <c r="O13" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L13" t="str">
+      <c r="P13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P13" t="str">
+      <c r="T13" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3280,39 +4273,51 @@
         <v>2024</v>
       </c>
       <c r="E14" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G14" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="F14" t="str">
+      <c r="H14" t="str">
         <v>body_material</v>
       </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I14" t="str">
+      <c r="K14" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
+        <v>player</v>
+      </c>
+      <c r="M14" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N14" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K14" t="str">
+      <c r="O14" t="str">
         <v>manual</v>
       </c>
-      <c r="L14" t="str">
+      <c r="P14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M14" t="str">
+      <c r="Q14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N14" t="str">
+      <c r="R14" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O14" t="str">
+      <c r="S14" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P14" t="str">
+      <c r="T14" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3330,39 +4335,51 @@
         <v>2024</v>
       </c>
       <c r="E15" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G15" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="F15" t="str">
+      <c r="H15" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>player</v>
+      </c>
+      <c r="M15" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N15" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K15" t="str">
+      <c r="O15" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L15" t="str">
+      <c r="P15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P15" t="str">
+      <c r="T15" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3380,39 +4397,51 @@
         <v>2024</v>
       </c>
       <c r="E16" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G16" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="F16" t="str">
+      <c r="H16" t="str">
         <v>body_material</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I16" t="str">
+      <c r="K16" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
+        <v>player</v>
+      </c>
+      <c r="M16" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N16" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K16" t="str">
+      <c r="O16" t="str">
         <v>manual</v>
       </c>
-      <c r="L16" t="str">
+      <c r="P16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M16" t="str">
+      <c r="Q16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N16" t="str">
+      <c r="R16" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O16" t="str">
+      <c r="S16" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P16" t="str">
+      <c r="T16" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3430,39 +4459,51 @@
         <v>2024</v>
       </c>
       <c r="E17" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G17" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="F17" t="str">
+      <c r="H17" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>player</v>
+      </c>
+      <c r="M17" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N17" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K17" t="str">
+      <c r="O17" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L17" t="str">
+      <c r="P17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P17" t="str">
+      <c r="T17" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3480,39 +4521,51 @@
         <v>2024</v>
       </c>
       <c r="E18" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G18" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="F18" t="str">
+      <c r="H18" t="str">
         <v>body_material</v>
       </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I18" t="str">
+      <c r="K18" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
+        <v>player</v>
+      </c>
+      <c r="M18" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N18" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K18" t="str">
+      <c r="O18" t="str">
         <v>manual</v>
       </c>
-      <c r="L18" t="str">
+      <c r="P18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M18" t="str">
+      <c r="Q18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N18" t="str">
+      <c r="R18" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O18" t="str">
+      <c r="S18" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P18" t="str">
+      <c r="T18" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3530,39 +4583,51 @@
         <v>2024</v>
       </c>
       <c r="E19" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G19" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="F19" t="str">
+      <c r="H19" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>player</v>
+      </c>
+      <c r="M19" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N19" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K19" t="str">
+      <c r="O19" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L19" t="str">
+      <c r="P19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P19" t="str">
+      <c r="T19" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3580,39 +4645,51 @@
         <v>2024</v>
       </c>
       <c r="E20" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G20" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="F20" t="str">
+      <c r="H20" t="str">
         <v>body_material</v>
       </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I20" t="str">
+      <c r="K20" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
+        <v>player</v>
+      </c>
+      <c r="M20" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N20" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K20" t="str">
+      <c r="O20" t="str">
         <v>manual</v>
       </c>
-      <c r="L20" t="str">
+      <c r="P20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M20" t="str">
+      <c r="Q20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N20" t="str">
+      <c r="R20" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O20" t="str">
+      <c r="S20" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P20" t="str">
+      <c r="T20" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3630,39 +4707,51 @@
         <v>2024</v>
       </c>
       <c r="E21" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G21" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="F21" t="str">
+      <c r="H21" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>player</v>
+      </c>
+      <c r="M21" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N21" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K21" t="str">
+      <c r="O21" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L21" t="str">
+      <c r="P21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P21" t="str">
+      <c r="T21" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3680,39 +4769,51 @@
         <v>2024</v>
       </c>
       <c r="E22" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G22" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>body_material</v>
       </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I22" t="str">
+      <c r="K22" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
+        <v>player</v>
+      </c>
+      <c r="M22" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N22" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K22" t="str">
+      <c r="O22" t="str">
         <v>manual</v>
       </c>
-      <c r="L22" t="str">
+      <c r="P22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="M22" t="str">
+      <c r="Q22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="N22" t="str">
+      <c r="R22" t="str">
         <v>Candidate is marketing/technology wording rather than the reviewed body material statement.</v>
       </c>
-      <c r="O22" t="str">
+      <c r="S22" t="str">
         <v>Bind to 2024 Metanium DC. Body material wording may differ across other Metanium DC years.</v>
       </c>
-      <c r="P22" t="str">
+      <c r="T22" t="str">
         <v>Manual override based on review knowledge: 2024 Metanium DC uses CORESOLID BODY magnesium one-piece body wording.</v>
       </c>
     </row>
@@ -3730,39 +4831,51 @@
         <v>2024</v>
       </c>
       <c r="E23" t="str">
+        <v>24 Metanium DC (digital control) Japan model 2024-</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Metanium DC | 2024 | 6 sku variants</v>
+      </c>
+      <c r="G23" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="F23" t="str">
+      <c r="H23" t="str">
         <v>gear_material</v>
       </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>player</v>
+      </c>
+      <c r="M23" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N23" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K23" t="str">
+      <c r="O23" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L23" t="str">
+      <c r="P23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
         <v>Bind to 2024 Metanium DC. Gear material may differ across other Metanium DC years.</v>
       </c>
-      <c r="P23" t="str">
+      <c r="T23" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3777,42 +4890,54 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E24" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F24" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G24" t="str">
         <v>CALCUTTA CONQUEST BFS HG RIGHT</v>
       </c>
-      <c r="F24" t="str">
+      <c r="H24" t="str">
         <v>body_material</v>
       </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="I24" t="str">
+      <c r="K24" t="str">
         <v>全加工</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
+        <v>player</v>
+      </c>
+      <c r="M24" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N24" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K24" t="str">
+      <c r="O24" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L24" t="str">
+      <c r="P24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="P24" t="str">
+      <c r="T24" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3827,42 +4952,54 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E25" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F25" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G25" t="str">
         <v>CALCUTTA CONQUEST BFS HG LEFT</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>body_material</v>
       </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="I25" t="str">
+      <c r="K25" t="str">
         <v>全加工</v>
       </c>
-      <c r="J25" t="str">
+      <c r="L25" t="str">
+        <v>player</v>
+      </c>
+      <c r="M25" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N25" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K25" t="str">
+      <c r="O25" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L25" t="str">
+      <c r="P25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="P25" t="str">
+      <c r="T25" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3877,42 +5014,54 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E26" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F26" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G26" t="str">
         <v>CALCUTTA CONQUEST BFS XG RIGHT</v>
       </c>
-      <c r="F26" t="str">
+      <c r="H26" t="str">
         <v>body_material</v>
       </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="I26" t="str">
+      <c r="K26" t="str">
         <v>全加工</v>
       </c>
-      <c r="J26" t="str">
+      <c r="L26" t="str">
+        <v>player</v>
+      </c>
+      <c r="M26" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N26" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K26" t="str">
+      <c r="O26" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L26" t="str">
+      <c r="P26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="P26" t="str">
+      <c r="T26" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3927,42 +5076,54 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E27" t="str">
+        <v>23 Calcutta Conquest BFS Japan model 2023- - Shimano - Casting Reels</v>
+      </c>
+      <c r="F27" t="str">
+        <v>CALCUTTA CONQUEST BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G27" t="str">
         <v>CALCUTTA CONQUEST BFS XG LEFT</v>
       </c>
-      <c r="F27" t="str">
+      <c r="H27" t="str">
         <v>body_material</v>
       </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
         <v>Aluminum</v>
       </c>
-      <c r="I27" t="str">
+      <c r="K27" t="str">
         <v>全加工</v>
       </c>
-      <c r="J27" t="str">
+      <c r="L27" t="str">
+        <v>player</v>
+      </c>
+      <c r="M27" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N27" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K27" t="str">
+      <c r="O27" t="str">
         <v>whitelist</v>
       </c>
-      <c r="L27" t="str">
+      <c r="P27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
         <v>Do not spread by model-only match. Keep reel_id and SKU binding until year/version is confirmed.</v>
       </c>
-      <c r="P27" t="str">
+      <c r="T27" t="str">
         <v>Future apply must keep reel_id + year/version + SKU binding.</v>
       </c>
     </row>
@@ -3977,42 +5138,54 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E28" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="F28" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G28" t="str">
         <v>ALDEBARAN BFS HG R</v>
       </c>
-      <c r="F28" t="str">
+      <c r="H28" t="str">
         <v>body_material</v>
       </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I28" t="str">
+      <c r="K28" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J28" t="str">
+      <c r="L28" t="str">
+        <v>player</v>
+      </c>
+      <c r="M28" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N28" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K28" t="str">
+      <c r="O28" t="str">
         <v>manual</v>
       </c>
-      <c r="L28" t="str">
+      <c r="P28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="M28" t="str">
+      <c r="Q28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="N28" t="str">
+      <c r="R28" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="O28" t="str">
+      <c r="S28" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="P28" t="str">
+      <c r="T28" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -4027,42 +5200,54 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E29" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="F29" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G29" t="str">
         <v>ALDEBARAN BFS HG L</v>
       </c>
-      <c r="F29" t="str">
+      <c r="H29" t="str">
         <v>body_material</v>
       </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I29" t="str">
+      <c r="K29" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
+        <v>player</v>
+      </c>
+      <c r="M29" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N29" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K29" t="str">
+      <c r="O29" t="str">
         <v>manual</v>
       </c>
-      <c r="L29" t="str">
+      <c r="P29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="M29" t="str">
+      <c r="Q29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="N29" t="str">
+      <c r="R29" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="O29" t="str">
+      <c r="S29" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="P29" t="str">
+      <c r="T29" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -4077,42 +5262,54 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E30" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="F30" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G30" t="str">
         <v>ALDEBARAN BFS XG R</v>
       </c>
-      <c r="F30" t="str">
+      <c r="H30" t="str">
         <v>body_material</v>
       </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I30" t="str">
+      <c r="K30" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J30" t="str">
+      <c r="L30" t="str">
+        <v>player</v>
+      </c>
+      <c r="M30" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N30" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K30" t="str">
+      <c r="O30" t="str">
         <v>manual</v>
       </c>
-      <c r="L30" t="str">
+      <c r="P30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="M30" t="str">
+      <c r="Q30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="N30" t="str">
+      <c r="R30" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="O30" t="str">
+      <c r="S30" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="P30" t="str">
+      <c r="T30" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
@@ -4127,48 +5324,60 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="E31" t="str">
+        <v>22 Aldebaran BFS, ultimate finesse 2.0g, 2022- - 2026 Spring Trout Special</v>
+      </c>
+      <c r="F31" t="str">
+        <v>ALDEBARAN BFS | 2026 | 4 sku variants</v>
+      </c>
+      <c r="G31" t="str">
         <v>ALDEBARAN BFS XG L</v>
       </c>
-      <c r="F31" t="str">
+      <c r="H31" t="str">
         <v>body_material</v>
       </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="I31" t="str">
+      <c r="K31" t="str">
         <v>HAGANE 机身</v>
       </c>
-      <c r="J31" t="str">
+      <c r="L31" t="str">
+        <v>player</v>
+      </c>
+      <c r="M31" t="str">
+        <v>official &gt; player</v>
+      </c>
+      <c r="N31" t="str">
         <v>fill_empty</v>
       </c>
-      <c r="K31" t="str">
+      <c r="O31" t="str">
         <v>manual</v>
       </c>
-      <c r="L31" t="str">
+      <c r="P31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="M31" t="str">
+      <c r="Q31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="N31" t="str">
+      <c r="R31" t="str">
         <v>Candidate is a technology/system phrase instead of a specific body material.</v>
       </c>
-      <c r="O31" t="str">
+      <c r="S31" t="str">
         <v>Aldebaran BFS body material must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
-      <c r="P31" t="str">
+      <c r="T31" t="str">
         <v>Manual override based on review knowledge: body wording should reflect Magnesium / HAGANE body, not 'Hagane body system'.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T31"/>
   </ignoredErrors>
 </worksheet>
 </file>